--- a/tools/importer/reports/import-who-we-are-topic.report.xlsx
+++ b/tools/importer/reports/import-who-we-are-topic.report.xlsx
@@ -124,7 +124,7 @@
     <t>who-we-are</t>
   </si>
   <si>
-    <t>2026-05-14T16:04:39.512Z</t>
+    <t>2026-05-15T20:01:30.755Z</t>
   </si>
   <si>
     <t>Who We Are — Chevron</t>
@@ -145,7 +145,7 @@
     <t>sustainability-topic</t>
   </si>
   <si>
-    <t>2026-05-15T12:47:15.848Z</t>
+    <t>2026-05-15T20:02:02.695Z</t>
   </si>
   <si>
     <t>Climate – Chevron.com — Chevron</t>
@@ -163,7 +163,7 @@
     <t>sustainability/environment</t>
   </si>
   <si>
-    <t>2026-05-15T12:47:22.628Z</t>
+    <t>2026-05-15T20:02:10.641Z</t>
   </si>
   <si>
     <t>Environment | Chevron — Chevron</t>
@@ -181,7 +181,7 @@
     <t>sustainability/social-investment</t>
   </si>
   <si>
-    <t>2026-05-15T12:48:15.982Z</t>
+    <t>2026-05-15T20:03:03.734Z</t>
   </si>
   <si>
     <t>Social Investment | Chevron — Chevron</t>
@@ -202,7 +202,7 @@
     <t>what-we-do-topic</t>
   </si>
   <si>
-    <t>2026-05-15T13:53:59.978Z</t>
+    <t>2026-05-15T20:01:40.940Z</t>
   </si>
   <si>
     <t>Energy Solutions — Chevron</t>
@@ -220,7 +220,7 @@
     <t>what-we-do/technology-and-innovation</t>
   </si>
   <si>
-    <t>2026-05-15T13:54:13.965Z</t>
+    <t>2026-05-15T20:01:52.392Z</t>
   </si>
   <si>
     <t>Technology and Innovation — Chevron</t>
@@ -241,7 +241,7 @@
     <t>who-we-are-topic</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:27.138Z</t>
+    <t>2026-05-15T20:03:13.653Z</t>
   </si>
   <si>
     <t>Chevron Culture — Chevron</t>
@@ -259,7 +259,7 @@
     <t>who-we-are/history</t>
   </si>
   <si>
-    <t>2026-05-15T15:35:01.308Z</t>
+    <t>2026-05-15T20:03:50.372Z</t>
   </si>
   <si>
     <t>Our History | Chevron — Chevron</t>
@@ -277,7 +277,7 @@
     <t>who-we-are/leadership</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:40.279Z</t>
+    <t>2026-05-15T20:03:29.275Z</t>
   </si>
   <si>
     <t>Chevron Leadership — Chevron</t>
@@ -295,7 +295,7 @@
     <t>who-we-are/our-brands</t>
   </si>
   <si>
-    <t>2026-05-15T15:34:33.105Z</t>
+    <t>2026-05-15T20:03:23.337Z</t>
   </si>
   <si>
     <t>Our Brands — Chevron</t>
